--- a/applications.xlsx
+++ b/applications.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="applied_jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="job_suggestions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,63 +447,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Last Update</t>
+          <t>Applied_Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Last_Update</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiter_Email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Email_Subject</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Days_Since_Update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Zetheta Algorithms Private Limited</t>
+          <t>Sornambal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ritika from Unstop &lt;noreply@dare2compete.news&gt;</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prepare for your next interview round of internship with top mentors, Sornambal</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICVASTGLOBE LLP</t>
+          <t>Indeed Ireland Operations Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Developer Intern (AI/Python + Angular)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied_Confirmation.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Indeed Application: Developer Intern (AI/Python + Angular)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Innovexis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oracle Infra Intern</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +584,2491 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Innovexis &lt;info@recooty.com&gt;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Application Received - Thank You!</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>WABRIC &lt;wabric.hr@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Submission of Offer Letter and NDA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>✓ Valid transition: Interview → Offer</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scholete AI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Scholete AI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unstop</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AI/ML Internship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Unstop Events &lt;updates@unstop.events&gt;</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Update on your application for AI/ML Internship!</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>none mentioned</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>none mentioned</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pine Talent Consultants &lt;alerts@jobs.shine.com&gt;</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[Interview Call] Profile Details Required</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VaidSys Technologies</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AI/ML Internship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Unstop Events &lt;updates@unstop.events&gt;</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Update on your application for AI/ML Internship!</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASHVATHA LABS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>video interview</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ASHVATHA LABS via Indeed &lt;no-reply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ASHVATHA LABS has canceled your video interview.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Rejected</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vulcury LLC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer (Hyderabad) - Calisade Asset Management</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sakshi Srivastava &lt;sakshi@vulcury.com&gt;</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Next Step in Your Application –AI / ML Engineer (Hyderabad) – Calisade Asset Management at Vulcury LLC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ASHVATHA LABS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Product Developer Inter</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Indeed &lt;no-reply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Reminder: Video interview tomorrow with ASHVATHA LABS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WAONIC FASHION PVT. LTD., BANGALORE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AI/ML Trainee</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WABRIC &lt;wabric.hr@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Re: Submission of Offer Letter and NDA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Rejected</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ritika from Unstop &lt;noreply@dare2compete.news&gt;</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Prepare for your next interview round of internship with top mentors, Sornambal</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indeed Ireland Operations Limited</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Indeed Application: AI Intern</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Waonic Fashion Private Limited</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AI/ML Trainee</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;sornambalp97@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Re: Submission of Offer Letter and NDA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Offer</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ASHVATHA LABS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Indeed &lt;no-reply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>You scheduled a video interview with ASHVATHA LABS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unknown/Not Provided in Email</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AI/ML Internship</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for AI/ML Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Zetheta Algorithms Private Limited</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>"Avani Shah, Zetheta Algorithms" &lt;hr@zetheta.in&gt;</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Reminder: Application Accepted for Live Project Internship</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Confirmed</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wabric</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Traineeship</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>WABRIC &lt;wabric.hr@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Appointment booked: Wabric Traineeship Interview (Sornambal P) @ Sun 4 Jan 2026 4pm - 4:20pm (IST) (sornambalp97@gmail.com)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kukbit SL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AIm/ML Internship</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Unstop Events &lt;updates@unstop.email&gt;</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Update on your application for AI/ML Internship!</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bluestock Fintech</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Software Development Engineer (SDE) Intern</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HR Team - Bluestock &lt;hr.b@team.bluestock.in&gt;</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Your Offer Letter - Important</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Offer</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SandBox HR Consultants &lt;alerts@jobs.shine.com&gt;</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Your Profile is Shortlisted! Details Required</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Wabric</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AI/ML Traineeship Program</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WABRIC &lt;wabric.hr@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Congratulations, You’ve Been Shortlisted for the Wabric AI/ML Traineeship Program 🎉</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Optimspace</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Optimspace &lt;info@recooty.com&gt;</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Application Received - Thank You!</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pine Talent Consultants &lt;alerts@jobs.shine.com&gt;</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[Interview Call] Profile Details Required</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TallyMet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fresher Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HR Department &lt;hr@tallymet.com&gt;</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Invitation for Interview - Fresher Artificial Intelligence Position</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Omrivya</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Irrelevant</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irrelevant.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Your application was viewed by Omrivya</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Irrelevant.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mercor</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - India</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mercor &lt;team@mercor.com&gt;</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Application Submitted - Machine Learning Engineer - India on Mercor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sornambal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>None specified</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ritika from Unstop &lt;noreply@dare2compete.news&gt;</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Prepare for your next interview round with top mentors, Sornambal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Internship</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Internship</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for AI/ML Engineer Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for AI/ML Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Optimspace</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Optimspace &lt;info@recooty.com&gt;</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Application Received - Thank You!</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CloudAILabs.in</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CloudAILabs Internship Program</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CloudAILabs &lt;hr@cloudailabs.in&gt;</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ACTION REQUIRED: Application Shortlisted - Internship Orientation</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hackathon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Application Approved</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SpeakSpace &lt;team@speakspace.co&gt;</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hackathon Application Approved</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Labmentix</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Labmentix HR &lt;swaraj@labmentix.in&gt;</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Next Steps for Your Application with Labmentix</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Wixflux Technologies</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Internship Program</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>hr@wixflux.in</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Congratulations! Your Profile Has Been Shortlisted – Internship Program</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Offer</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Woject Technologies</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Woject Technologies HR &lt;hr@woject.com&gt;</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Your Offer Letter - Woject Technologies</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Offer</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BluMotiv</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Connect &lt;connect@blumotiv.com&gt;</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thank You for Applying for the Data Science Intern Role at BluMotiv</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HDFC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Scholarship</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Team Unstop &lt;noreply@dare2compete.news&gt;</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>🎉 Congrats! You’re shortlisted for HDFC Scholarship 2025-26</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Developer Internship</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for Artificial Intelligence Developer Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Data Analyst Internship</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for Data Analyst Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Science Internship</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for Data Science Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hearty congratulations on your Data Science &amp; Analytics Internship</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;sornambalp97@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fwd: Hearty congratulations on your Data Science &amp; Analytics Internship Offer!</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Offer</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Innovara Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Careers - InnovaraTech &lt;careers@innovaratech.in&gt;</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Re: Data Analyst Application – Assessment Invitation</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LLM Sourcing</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Data Scientist/Analyst (Remote)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vikram Bagga &lt;vikramjit.b@turing.com&gt;</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>⚡ Quick Reminder: Your Application Needs One Last Step!</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Applied_Confirmation</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Trainee Manager</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Landmark Global &lt;opportunities@foundit.in&gt;</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>WALK-IN-INTERVIEW// TRAINEE MANAGER</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Initial application detected via: Interview</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Email_Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Saved</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>From: Pooja from foundit &lt;jobmessenger@monsterindia.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VISTA APPLIED SOLUTIONS GROUP INC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Is Hiring: Find Out Why You Should Apply</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>From: Aditi &lt;noreply@jobeka.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rearc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sikich India</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AI Agent Developer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>From: LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Glance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II- Recommendation Systems</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>From: LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SuperKalam</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AI/ML research (Internship)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>From: Y Combinator &lt;workatastartup@ycombinator.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>From: Sneha from foundit &lt;jobmessenger@monsterindia.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>jobs that you haven't applied yet but others are applying</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>From: Sneha from foundit &lt;jobmessenger@monsterindia.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Codeguardian Tech International Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Opportunity: Mobile Application Development Intern (Remote)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mobile Application Development Intern</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>From: Stuti from Abekus &lt;hello@abekus.co&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI / ML Associate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BuzzBoard</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LLMs and Applied Machine Learning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L’Oréal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brandstorm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>From: Janvi from Unstop &lt;noreply@dare2compete.news&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Base0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data Scientist/Analyst</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>From: Turing &lt;communications@turing.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>top AI-based company</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data Scientist/Analyst</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>From: Turing &lt;communications@turing.com&gt;</t>
         </is>
       </c>
     </row>

--- a/applications.xlsx
+++ b/applications.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1698,22 +1698,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mercor &lt;team@mercor.com&gt;</t>
+          <t>Mercor &lt;no-reply@mercor.com&gt;</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Application Submitted - Machine Learning Engineer - India on Mercor</t>
+          <t>Update on your application for Machine Learning Engineer - India</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Initial application detected via: Applied_Confirmation</t>
+          <t>✓ Valid transition: Applied → Rejected</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2519,6 +2519,1318 @@
         </is>
       </c>
       <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Company not available in the given email snippet</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AI Engineer Internship</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Relevant</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Unstop &lt;noreply@emails.unstop.com&gt;</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Congratulations! Your application for AI Engineer Internship is complete!</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Indeed Ireland Operations Limited</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Indeed Application: AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer (Gurugram)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Indeed Application: AI / ML Engineer (Gurugram) – Calisade Asset Management</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Machine Learning Internship</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Autonomize Hiring team &lt;no-reply@kekamail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Application for Machine Learning Internship received, Thank you!</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Indeed Ireland Operations Limited</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Machine Learning Internship</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Indeed Application: Machine Learning Internship</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Insight Global</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Insight Global</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MightyBot</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to MightyBot</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Internshala (Scholiverse Educare Pvt. Ltd.)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Skills Assessment</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Internshala &lt;student@internshala.com&gt;</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Deadline Approaching! Interview Invite from Aadhvik Technologies</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Labmentix</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>no available information provided</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HR Labmentix &lt;swaraj@labmentix.in&gt;</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Next Steps for Your Application with Labmentix</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aadhvik Technologies</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Machine Learning Internship</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Internshala &lt;student@internshala.com&gt;</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Interview Invite from Aadhvik Technologies for Machine Learning Internship</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Vedika API</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Intern</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Vedika API</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Applogic Development pvt ltd.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Your application to Generative AI Engineer at Applogic Development pvt ltd.,</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>✓ Valid transition: Applied → Rejected</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;noreply@curately.ai&gt;</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We Received Your Application for AI/ML Engineer at Demo </t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Saker</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Computer Vision / AI Intern</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Saker</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Etenico Technologies</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Etenico Technologies</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Insight Global</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Applied_Confirmation.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Insight Global</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Hatch</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to Data Hatch</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TechKnowledgeHub.org</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Generative AI Developer Interns</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sornambal, your application was sent to TechKnowledgeHub.org</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Indeed Ireland Operations Limited</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AI ENGINEER — Generative AI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Indeed Application: AI ENGINEER — Generative AI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Advice Media</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AI ENGINEER — Generative AI</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MyAdvice &lt;noreply@applytojob.com&gt;</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Application Received |  AI ENGINEER — Generative AI with Advice Media</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Indeed Ireland Operations Limited</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Indeed Apply &lt;indeedapply@indeed.com&gt;</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Indeed Application: AI Engineer</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Stackular</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Rejected.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Your application to AI/ML Intern – Agentic AI (Autonomous Agents) at Stackular</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>scombinator26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AI Agents – Social Media Automation</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S Combinator &lt;scombinator26@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Interview Invitation - AI Agents Social Media Automation Internship</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Vulcury LLC</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer (Pune) – Calisade Asset Management</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sakshi Srivastava &lt;sakshi@vulcury.com&gt;</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Next Step in Your Application – AI / ML Engineer (Pune) – Calisade Asset Management at Vulcury LLC</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Linksoft Technologies</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>JobRecommendation</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>LinkedIn Job Alerts &lt;jobalerts-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>“python developer”: Linksoft Technologies - AI Application Engineer and more</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S Combinator</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AI Agents - Social Media Automation Internship</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;sornambalp97@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Re: Quick Update Request – AI Agents Internship Interview</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AI Agents – Social Media Automation Internship</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S Combinator &lt;scombinator26@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Re: Quick Update Request – AI Agents Internship Interview</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI Agents</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Social Media Automation Internship</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;sornambalp97@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Quick Update Request – AI Agents Internship Interview</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>S Combinator</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AI Agents – Social Media Automation internship</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sornambal P &lt;sornambalp97@gmail.com&gt;</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Quick Update Request – AI Agents Internship Interview
+Hello Sujith,
+Hope you’re doing well.
+I wanted to check in regarding the interview outcome for the AI Agents – Social Media Automation internship. As mentioned, you had shared that the results would be communicated by Friday.
+I wanted to let you know that I’ve received another internship offer, with a deadline to confirm by tomorrow. Before proceeding, I wanted to check if there is any update from your side.
+Thank you once again for the conversation and opportunity. I look forward to hearing from you.
+Best regards,  
+Sornambal</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>New application detected</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2533,7 +3845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3072,6 +4384,134 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brainwonders</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AI Research (Freelancer)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>From: Brainwonders &lt;notification@smartrecruiters.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fusemachines</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AI Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Curately AI, Inc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>From: LinkedIn &lt;jobs-noreply@linkedin.com&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fusemachines</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AI Automation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>From: Glassdoor Jobs &lt;noreply@glassdoor.com&gt;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
